--- a/data/Working.xlsx
+++ b/data/Working.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dev\C#\ffxiv-lang-swap\LangSwap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A332DA7F-3050-4B99-8D92-26A050805B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304697AA-D156-4763-A773-0A8D055B0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Working" sheetId="10" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="976">
   <si>
     <t>_rsv_46188_-1_3_0_0_SE2DC5B04_EE2DC5B04</t>
   </si>
@@ -2917,6 +2917,42 @@
   </si>
   <si>
     <t>_rsv_47038_-1_3_0_1_SE2DC5B04_EE2DC5B04</t>
+  </si>
+  <si>
+    <t>Streuschall</t>
+  </si>
+  <si>
+    <t>Fokusschall</t>
+  </si>
+  <si>
+    <t>_rsv_47235_-1_2_0_1_SE2DC5B04_EE2DC5B04</t>
+  </si>
+  <si>
+    <t>_rsv_45980_-1_2_0_0_SE2DC5B04_EE2DC5B04</t>
+  </si>
+  <si>
+    <t>_rsv_45981_-1_2_0_0_SE2DC5B04_EE2DC5B04</t>
+  </si>
+  <si>
+    <t>_rsv_45982_-1_2_0_0_SE2DC5B04_EE2DC5B04</t>
+  </si>
+  <si>
+    <t>_rsv_45983_-1_2_0_0_SE2DC5B04_EE2DC5B04</t>
+  </si>
+  <si>
+    <t>_rsv_47235_-1_2_0_0_SE2DC5B04_EE2DC5B04</t>
+  </si>
+  <si>
+    <t>_rsv_45980_-1_2_0_1_SE2DC5B04_EE2DC5B04</t>
+  </si>
+  <si>
+    <t>_rsv_45981_-1_2_0_1_SE2DC5B04_EE2DC5B04</t>
+  </si>
+  <si>
+    <t>_rsv_45982_-1_2_0_1_SE2DC5B04_EE2DC5B04</t>
+  </si>
+  <si>
+    <t>_rsv_45983_-1_2_0_1_SE2DC5B04_EE2DC5B04</t>
   </si>
 </sst>
 </file>
@@ -3177,6 +3213,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCF5996-96C7-4F1D-A605-6E9737076FC7}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="11.42578125" customWidth="1"/>
+  </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7315,7 +7354,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C176"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -7325,1396 +7364,1396 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1">
-        <v>45953</v>
+        <v>45980</v>
       </c>
       <c r="B1" t="s">
-        <v>619</v>
+        <v>967</v>
       </c>
       <c r="C1" t="s">
-        <v>620</v>
+        <v>964</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>45954</v>
+        <v>45981</v>
       </c>
       <c r="B2" t="s">
-        <v>621</v>
+        <v>968</v>
       </c>
       <c r="C2" t="s">
-        <v>622</v>
+        <v>965</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>46508</v>
+        <v>45982</v>
       </c>
       <c r="B3" t="s">
-        <v>623</v>
+        <v>969</v>
       </c>
       <c r="C3" t="s">
-        <v>624</v>
+        <v>964</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>46509</v>
+        <v>45983</v>
       </c>
       <c r="B4" t="s">
-        <v>625</v>
+        <v>970</v>
       </c>
       <c r="C4" t="s">
-        <v>626</v>
+        <v>965</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>46510</v>
+        <v>47235</v>
       </c>
       <c r="B5" t="s">
-        <v>627</v>
+        <v>971</v>
       </c>
       <c r="C5" t="s">
-        <v>628</v>
+        <v>964</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>46511</v>
+        <v>45980</v>
       </c>
       <c r="B6" t="s">
-        <v>629</v>
+        <v>972</v>
       </c>
       <c r="C6" t="s">
-        <v>630</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>46512</v>
+        <v>45981</v>
       </c>
       <c r="B7" t="s">
-        <v>631</v>
+        <v>973</v>
       </c>
       <c r="C7" t="s">
-        <v>632</v>
+        <v>965</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>46513</v>
+        <v>45982</v>
       </c>
       <c r="B8" t="s">
-        <v>633</v>
+        <v>974</v>
       </c>
       <c r="C8" t="s">
-        <v>632</v>
+        <v>964</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>46514</v>
+        <v>45983</v>
       </c>
       <c r="B9" t="s">
-        <v>634</v>
+        <v>975</v>
       </c>
       <c r="C9" t="s">
-        <v>635</v>
+        <v>965</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>46515</v>
+        <v>47235</v>
       </c>
       <c r="B10" t="s">
-        <v>636</v>
+        <v>966</v>
       </c>
       <c r="C10" t="s">
-        <v>635</v>
+        <v>964</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>46516</v>
+        <v>45953</v>
       </c>
       <c r="B11" t="s">
-        <v>637</v>
+        <v>619</v>
       </c>
       <c r="C11" t="s">
-        <v>635</v>
+        <v>620</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>46517</v>
+        <v>45954</v>
       </c>
       <c r="B12" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="C12" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>46547</v>
+        <v>46508</v>
       </c>
       <c r="B13" t="s">
-        <v>639</v>
+        <v>623</v>
       </c>
       <c r="C13" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>46550</v>
+        <v>46509</v>
       </c>
       <c r="B14" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="C14" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>46557</v>
+        <v>46510</v>
       </c>
       <c r="B15" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="C15" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>46558</v>
+        <v>46511</v>
       </c>
       <c r="B16" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C16" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>46559</v>
+        <v>46512</v>
       </c>
       <c r="B17" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="C17" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>46560</v>
+        <v>46513</v>
       </c>
       <c r="B18" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="C18" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>46561</v>
+        <v>46514</v>
       </c>
       <c r="B19" t="s">
-        <v>649</v>
+        <v>634</v>
       </c>
       <c r="C19" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>46562</v>
+        <v>46515</v>
       </c>
       <c r="B20" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="C20" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>46575</v>
+        <v>46516</v>
       </c>
       <c r="B21" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="C21" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>46576</v>
+        <v>46517</v>
       </c>
       <c r="B22" t="s">
-        <v>653</v>
+        <v>638</v>
       </c>
       <c r="C22" t="s">
-        <v>654</v>
+        <v>635</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>46577</v>
+        <v>46547</v>
       </c>
       <c r="B23" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="C23" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>46578</v>
+        <v>46550</v>
       </c>
       <c r="B24" t="s">
-        <v>656</v>
+        <v>641</v>
       </c>
       <c r="C24" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>46579</v>
+        <v>46557</v>
       </c>
       <c r="B25" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="C25" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>46580</v>
+        <v>46558</v>
       </c>
       <c r="B26" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="C26" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>46581</v>
+        <v>46559</v>
       </c>
       <c r="B27" t="s">
-        <v>661</v>
+        <v>646</v>
       </c>
       <c r="C27" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>46582</v>
+        <v>46560</v>
       </c>
       <c r="B28" t="s">
-        <v>662</v>
+        <v>647</v>
       </c>
       <c r="C28" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>46583</v>
+        <v>46561</v>
       </c>
       <c r="B29" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="C29" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>46584</v>
+        <v>46562</v>
       </c>
       <c r="B30" t="s">
-        <v>665</v>
+        <v>650</v>
       </c>
       <c r="C30" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>46585</v>
+        <v>46575</v>
       </c>
       <c r="B31" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="C31" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>46586</v>
+        <v>46576</v>
       </c>
       <c r="B32" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="C32" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>47249</v>
+        <v>46577</v>
       </c>
       <c r="B33" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="C33" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>47250</v>
+        <v>46578</v>
       </c>
       <c r="B34" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="C34" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>45953</v>
+        <v>46579</v>
       </c>
       <c r="B35" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="C35" t="s">
-        <v>620</v>
+        <v>658</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>45954</v>
+        <v>46580</v>
       </c>
       <c r="B36" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="C36" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>46508</v>
+        <v>46581</v>
       </c>
       <c r="B37" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="C37" t="s">
-        <v>624</v>
+        <v>658</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>46509</v>
+        <v>46582</v>
       </c>
       <c r="B38" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="C38" t="s">
-        <v>626</v>
+        <v>660</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>46510</v>
+        <v>46583</v>
       </c>
       <c r="B39" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="C39" t="s">
-        <v>628</v>
+        <v>664</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>46511</v>
+        <v>46584</v>
       </c>
       <c r="B40" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="C40" t="s">
-        <v>630</v>
+        <v>666</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>46512</v>
+        <v>46585</v>
       </c>
       <c r="B41" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="C41" t="s">
-        <v>632</v>
+        <v>664</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>46513</v>
+        <v>46586</v>
       </c>
       <c r="B42" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="C42" t="s">
-        <v>632</v>
+        <v>666</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>46514</v>
+        <v>47249</v>
       </c>
       <c r="B43" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="C43" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>46515</v>
+        <v>47250</v>
       </c>
       <c r="B44" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="C44" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>46516</v>
+        <v>45953</v>
       </c>
       <c r="B45" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="C45" t="s">
-        <v>635</v>
+        <v>620</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>46517</v>
+        <v>45954</v>
       </c>
       <c r="B46" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="C46" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>46547</v>
+        <v>46508</v>
       </c>
       <c r="B47" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="C47" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>46550</v>
+        <v>46509</v>
       </c>
       <c r="B48" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C48" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>46557</v>
+        <v>46510</v>
       </c>
       <c r="B49" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C49" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>46558</v>
+        <v>46511</v>
       </c>
       <c r="B50" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="C50" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>46559</v>
+        <v>46512</v>
       </c>
       <c r="B51" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="C51" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>46560</v>
+        <v>46513</v>
       </c>
       <c r="B52" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="C52" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>46561</v>
+        <v>46514</v>
       </c>
       <c r="B53" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="C53" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>46562</v>
+        <v>46515</v>
       </c>
       <c r="B54" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="C54" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>46575</v>
+        <v>46516</v>
       </c>
       <c r="B55" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="C55" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>46576</v>
+        <v>46517</v>
       </c>
       <c r="B56" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="C56" t="s">
-        <v>654</v>
+        <v>635</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>46577</v>
+        <v>46547</v>
       </c>
       <c r="B57" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="C57" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>46578</v>
+        <v>46550</v>
       </c>
       <c r="B58" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="C58" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>46579</v>
+        <v>46557</v>
       </c>
       <c r="B59" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="C59" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>46580</v>
+        <v>46558</v>
       </c>
       <c r="B60" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="C60" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>46581</v>
+        <v>46559</v>
       </c>
       <c r="B61" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="C61" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>46582</v>
+        <v>46560</v>
       </c>
       <c r="B62" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="C62" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>46583</v>
+        <v>46561</v>
       </c>
       <c r="B63" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="C63" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>46584</v>
+        <v>46562</v>
       </c>
       <c r="B64" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="C64" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>46585</v>
+        <v>46575</v>
       </c>
       <c r="B65" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C65" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>46586</v>
+        <v>46576</v>
       </c>
       <c r="B66" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="C66" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>47249</v>
+        <v>46577</v>
       </c>
       <c r="B67" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="C67" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>47250</v>
+        <v>46578</v>
       </c>
       <c r="B68" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="C68" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>46139</v>
+        <v>46579</v>
       </c>
       <c r="B69" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="C69" t="s">
-        <v>706</v>
+        <v>658</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>46140</v>
+        <v>46580</v>
       </c>
       <c r="B70" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="C70" t="s">
-        <v>706</v>
+        <v>660</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>46170</v>
+        <v>46581</v>
       </c>
       <c r="B71" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="C71" t="s">
-        <v>709</v>
+        <v>658</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>46171</v>
+        <v>46582</v>
       </c>
       <c r="B72" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="C72" t="s">
-        <v>709</v>
+        <v>660</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>47037</v>
+        <v>46583</v>
       </c>
       <c r="B73" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="C73" t="s">
-        <v>712</v>
+        <v>664</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>47038</v>
+        <v>46584</v>
       </c>
       <c r="B74" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="C74" t="s">
-        <v>712</v>
+        <v>666</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>46139</v>
+        <v>46585</v>
       </c>
       <c r="B75" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="C75" t="s">
-        <v>706</v>
+        <v>664</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>46140</v>
+        <v>46586</v>
       </c>
       <c r="B76" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="C76" t="s">
-        <v>706</v>
+        <v>666</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>46170</v>
+        <v>47249</v>
       </c>
       <c r="B77" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="C77" t="s">
-        <v>709</v>
+        <v>640</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>46171</v>
+        <v>47250</v>
       </c>
       <c r="B78" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="C78" t="s">
-        <v>709</v>
+        <v>642</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>47037</v>
+        <v>46139</v>
       </c>
       <c r="B79" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="C79" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>47038</v>
+        <v>46140</v>
       </c>
       <c r="B80" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="C80" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>46188</v>
+        <v>46170</v>
       </c>
       <c r="B81" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="C81" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>46252</v>
+        <v>46171</v>
       </c>
       <c r="B82" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="C82" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>46253</v>
+        <v>47037</v>
       </c>
       <c r="B83" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="C83" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>46287</v>
+        <v>47038</v>
       </c>
       <c r="B84" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="C84" t="s">
-        <v>727</v>
+        <v>712</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>46288</v>
+        <v>46139</v>
       </c>
       <c r="B85" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="C85" t="s">
-        <v>727</v>
+        <v>706</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>46296</v>
+        <v>46140</v>
       </c>
       <c r="B86" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="C86" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>46305</v>
+        <v>46170</v>
       </c>
       <c r="B87" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="C87" t="s">
-        <v>731</v>
+        <v>709</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>46307</v>
+        <v>46171</v>
       </c>
       <c r="B88" t="s">
-        <v>732</v>
+        <v>717</v>
       </c>
       <c r="C88" t="s">
-        <v>733</v>
+        <v>709</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>46308</v>
+        <v>47037</v>
       </c>
       <c r="B89" t="s">
-        <v>734</v>
+        <v>718</v>
       </c>
       <c r="C89" t="s">
-        <v>733</v>
+        <v>712</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>46313</v>
+        <v>47038</v>
       </c>
       <c r="B90" t="s">
-        <v>735</v>
+        <v>719</v>
       </c>
       <c r="C90" t="s">
-        <v>736</v>
+        <v>712</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91">
-        <v>46314</v>
+        <v>46188</v>
       </c>
       <c r="B91" t="s">
-        <v>737</v>
+        <v>720</v>
       </c>
       <c r="C91" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92">
-        <v>46316</v>
+        <v>46252</v>
       </c>
       <c r="B92" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="C92" t="s">
-        <v>739</v>
+        <v>723</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>46322</v>
+        <v>46253</v>
       </c>
       <c r="B93" t="s">
-        <v>740</v>
+        <v>724</v>
       </c>
       <c r="C93" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>46323</v>
+        <v>46287</v>
       </c>
       <c r="B94" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="C94" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95">
-        <v>46326</v>
+        <v>46288</v>
       </c>
       <c r="B95" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="C95" t="s">
-        <v>745</v>
+        <v>727</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>46327</v>
+        <v>46296</v>
       </c>
       <c r="B96" t="s">
-        <v>746</v>
+        <v>729</v>
       </c>
       <c r="C96" t="s">
-        <v>747</v>
+        <v>721</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97">
-        <v>46328</v>
+        <v>46305</v>
       </c>
       <c r="B97" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="C97" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98">
-        <v>46329</v>
+        <v>46307</v>
       </c>
       <c r="B98" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="C98" t="s">
-        <v>751</v>
+        <v>733</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99">
-        <v>46330</v>
+        <v>46308</v>
       </c>
       <c r="B99" t="s">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="C99" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100">
-        <v>46331</v>
+        <v>46313</v>
       </c>
       <c r="B100" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="C100" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101">
-        <v>46334</v>
+        <v>46314</v>
       </c>
       <c r="B101" t="s">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="C101" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>46336</v>
+        <v>46316</v>
       </c>
       <c r="B102" t="s">
-        <v>758</v>
+        <v>738</v>
       </c>
       <c r="C102" t="s">
-        <v>759</v>
+        <v>739</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>46337</v>
+        <v>46322</v>
       </c>
       <c r="B103" t="s">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="C103" t="s">
-        <v>761</v>
+        <v>741</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>46338</v>
+        <v>46323</v>
       </c>
       <c r="B104" t="s">
-        <v>762</v>
+        <v>742</v>
       </c>
       <c r="C104" t="s">
-        <v>763</v>
+        <v>743</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>46339</v>
+        <v>46326</v>
       </c>
       <c r="B105" t="s">
-        <v>764</v>
+        <v>744</v>
       </c>
       <c r="C105" t="s">
-        <v>765</v>
+        <v>745</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>46340</v>
+        <v>46327</v>
       </c>
       <c r="B106" t="s">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="C106" t="s">
-        <v>767</v>
+        <v>747</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>46341</v>
+        <v>46328</v>
       </c>
       <c r="B107" t="s">
-        <v>768</v>
+        <v>748</v>
       </c>
       <c r="C107" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108">
-        <v>46345</v>
+        <v>46329</v>
       </c>
       <c r="B108" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="C108" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109">
-        <v>46364</v>
+        <v>46330</v>
       </c>
       <c r="B109" t="s">
-        <v>772</v>
+        <v>752</v>
       </c>
       <c r="C109" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110">
-        <v>46368</v>
+        <v>46331</v>
       </c>
       <c r="B110" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="C110" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111">
-        <v>46369</v>
+        <v>46334</v>
       </c>
       <c r="B111" t="s">
-        <v>776</v>
+        <v>756</v>
       </c>
       <c r="C111" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112">
-        <v>46370</v>
+        <v>46336</v>
       </c>
       <c r="B112" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="C112" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113">
-        <v>46371</v>
+        <v>46337</v>
       </c>
       <c r="B113" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="C113" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>46372</v>
+        <v>46338</v>
       </c>
       <c r="B114" t="s">
-        <v>779</v>
+        <v>762</v>
       </c>
       <c r="C114" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>46373</v>
+        <v>46339</v>
       </c>
       <c r="B115" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="C115" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>46377</v>
+        <v>46340</v>
       </c>
       <c r="B116" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="C116" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117">
-        <v>46378</v>
+        <v>46341</v>
       </c>
       <c r="B117" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="C117" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118">
-        <v>46379</v>
+        <v>46345</v>
       </c>
       <c r="B118" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="C118" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119">
-        <v>46380</v>
+        <v>46364</v>
       </c>
       <c r="B119" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="C119" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120">
-        <v>46381</v>
+        <v>46368</v>
       </c>
       <c r="B120" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="C120" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121">
-        <v>46382</v>
+        <v>46369</v>
       </c>
       <c r="B121" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="C121" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122">
-        <v>46383</v>
+        <v>46370</v>
       </c>
       <c r="B122" t="s">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="C122" t="s">
-        <v>793</v>
+        <v>775</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>46384</v>
+        <v>46371</v>
       </c>
       <c r="B123" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="C123" t="s">
-        <v>795</v>
+        <v>775</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>46392</v>
+        <v>46372</v>
       </c>
       <c r="B124" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="C124" t="s">
-        <v>797</v>
+        <v>775</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>46393</v>
+        <v>46373</v>
       </c>
       <c r="B125" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="C125" t="s">
-        <v>797</v>
+        <v>775</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126">
-        <v>46394</v>
+        <v>46377</v>
       </c>
       <c r="B126" t="s">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="C126" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>47577</v>
+        <v>46378</v>
       </c>
       <c r="B127" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="C127" t="s">
         <v>782</v>
@@ -8722,527 +8761,527 @@
     </row>
     <row r="128" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>48098</v>
+        <v>46379</v>
       </c>
       <c r="B128" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
       <c r="C128" t="s">
-        <v>802</v>
+        <v>785</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129">
-        <v>46188</v>
+        <v>46380</v>
       </c>
       <c r="B129" t="s">
-        <v>803</v>
+        <v>786</v>
       </c>
       <c r="C129" t="s">
-        <v>721</v>
+        <v>787</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>46252</v>
+        <v>46381</v>
       </c>
       <c r="B130" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="C130" t="s">
-        <v>723</v>
+        <v>789</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131">
-        <v>46253</v>
+        <v>46382</v>
       </c>
       <c r="B131" t="s">
-        <v>805</v>
+        <v>790</v>
       </c>
       <c r="C131" t="s">
-        <v>725</v>
+        <v>791</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>46287</v>
+        <v>46383</v>
       </c>
       <c r="B132" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="C132" t="s">
-        <v>727</v>
+        <v>793</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>46288</v>
+        <v>46384</v>
       </c>
       <c r="B133" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="C133" t="s">
-        <v>727</v>
+        <v>795</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>46296</v>
+        <v>46392</v>
       </c>
       <c r="B134" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="C134" t="s">
-        <v>721</v>
+        <v>797</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>46305</v>
+        <v>46393</v>
       </c>
       <c r="B135" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="C135" t="s">
-        <v>731</v>
+        <v>797</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>46307</v>
+        <v>46394</v>
       </c>
       <c r="B136" t="s">
-        <v>810</v>
+        <v>799</v>
       </c>
       <c r="C136" t="s">
-        <v>733</v>
+        <v>797</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>46308</v>
+        <v>47577</v>
       </c>
       <c r="B137" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="C137" t="s">
-        <v>733</v>
+        <v>782</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138">
-        <v>46313</v>
+        <v>48098</v>
       </c>
       <c r="B138" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
       <c r="C138" t="s">
-        <v>736</v>
+        <v>802</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139">
-        <v>46314</v>
+        <v>46188</v>
       </c>
       <c r="B139" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="C139" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140">
-        <v>46316</v>
+        <v>46252</v>
       </c>
       <c r="B140" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="C140" t="s">
-        <v>739</v>
+        <v>723</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>46322</v>
+        <v>46253</v>
       </c>
       <c r="B141" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="C141" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>46323</v>
+        <v>46287</v>
       </c>
       <c r="B142" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="C142" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143">
-        <v>46326</v>
+        <v>46288</v>
       </c>
       <c r="B143" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
       <c r="C143" t="s">
-        <v>745</v>
+        <v>727</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>46327</v>
+        <v>46296</v>
       </c>
       <c r="B144" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="C144" t="s">
-        <v>747</v>
+        <v>721</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>46328</v>
+        <v>46305</v>
       </c>
       <c r="B145" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="C145" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146">
-        <v>46329</v>
+        <v>46307</v>
       </c>
       <c r="B146" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="C146" t="s">
-        <v>751</v>
+        <v>733</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>46330</v>
+        <v>46308</v>
       </c>
       <c r="B147" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="C147" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148">
-        <v>46331</v>
+        <v>46313</v>
       </c>
       <c r="B148" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="C148" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>46334</v>
+        <v>46314</v>
       </c>
       <c r="B149" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
       <c r="C149" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150">
-        <v>46336</v>
+        <v>46316</v>
       </c>
       <c r="B150" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="C150" t="s">
-        <v>759</v>
+        <v>739</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151">
-        <v>46337</v>
+        <v>46322</v>
       </c>
       <c r="B151" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="C151" t="s">
-        <v>761</v>
+        <v>741</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152">
-        <v>46338</v>
+        <v>46323</v>
       </c>
       <c r="B152" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="C152" t="s">
-        <v>763</v>
+        <v>743</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153">
-        <v>46339</v>
+        <v>46326</v>
       </c>
       <c r="B153" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="C153" t="s">
-        <v>765</v>
+        <v>745</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154">
-        <v>46340</v>
+        <v>46327</v>
       </c>
       <c r="B154" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="C154" t="s">
-        <v>767</v>
+        <v>747</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155">
-        <v>46341</v>
+        <v>46328</v>
       </c>
       <c r="B155" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="C155" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156">
-        <v>46345</v>
+        <v>46329</v>
       </c>
       <c r="B156" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="C156" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157">
-        <v>46364</v>
+        <v>46330</v>
       </c>
       <c r="B157" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="C157" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158">
-        <v>46368</v>
+        <v>46331</v>
       </c>
       <c r="B158" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="C158" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159">
-        <v>46369</v>
+        <v>46334</v>
       </c>
       <c r="B159" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="C159" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160">
-        <v>46370</v>
+        <v>46336</v>
       </c>
       <c r="B160" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="C160" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161">
-        <v>46371</v>
+        <v>46337</v>
       </c>
       <c r="B161" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="C161" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162">
-        <v>46372</v>
+        <v>46338</v>
       </c>
       <c r="B162" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="C162" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>46373</v>
+        <v>46339</v>
       </c>
       <c r="B163" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="C163" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164">
-        <v>46377</v>
+        <v>46340</v>
       </c>
       <c r="B164" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="C164" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165">
-        <v>46378</v>
+        <v>46341</v>
       </c>
       <c r="B165" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="C165" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166">
-        <v>46379</v>
+        <v>46345</v>
       </c>
       <c r="B166" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="C166" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167">
-        <v>46380</v>
+        <v>46364</v>
       </c>
       <c r="B167" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="C167" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168">
-        <v>46381</v>
+        <v>46368</v>
       </c>
       <c r="B168" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="C168" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169">
-        <v>46382</v>
+        <v>46369</v>
       </c>
       <c r="B169" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="C169" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170">
-        <v>46383</v>
+        <v>46370</v>
       </c>
       <c r="B170" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="C170" t="s">
-        <v>793</v>
+        <v>775</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171">
-        <v>46384</v>
+        <v>46371</v>
       </c>
       <c r="B171" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
       <c r="C171" t="s">
-        <v>795</v>
+        <v>775</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172">
-        <v>46392</v>
+        <v>46372</v>
       </c>
       <c r="B172" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="C172" t="s">
-        <v>797</v>
+        <v>775</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173">
-        <v>46393</v>
+        <v>46373</v>
       </c>
       <c r="B173" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="C173" t="s">
-        <v>797</v>
+        <v>775</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174">
-        <v>46394</v>
+        <v>46377</v>
       </c>
       <c r="B174" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="C174" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175">
-        <v>47577</v>
+        <v>46378</v>
       </c>
       <c r="B175" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="C175" t="s">
         <v>782</v>
@@ -9250,12 +9289,122 @@
     </row>
     <row r="176" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176">
+        <v>46379</v>
+      </c>
+      <c r="B176" t="s">
+        <v>840</v>
+      </c>
+      <c r="C176" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>46380</v>
+      </c>
+      <c r="B177" t="s">
+        <v>841</v>
+      </c>
+      <c r="C177" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>46381</v>
+      </c>
+      <c r="B178" t="s">
+        <v>842</v>
+      </c>
+      <c r="C178" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>46382</v>
+      </c>
+      <c r="B179" t="s">
+        <v>843</v>
+      </c>
+      <c r="C179" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>46383</v>
+      </c>
+      <c r="B180" t="s">
+        <v>844</v>
+      </c>
+      <c r="C180" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>46384</v>
+      </c>
+      <c r="B181" t="s">
+        <v>845</v>
+      </c>
+      <c r="C181" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>46392</v>
+      </c>
+      <c r="B182" t="s">
+        <v>846</v>
+      </c>
+      <c r="C182" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>46393</v>
+      </c>
+      <c r="B183" t="s">
+        <v>847</v>
+      </c>
+      <c r="C183" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>46394</v>
+      </c>
+      <c r="B184" t="s">
+        <v>848</v>
+      </c>
+      <c r="C184" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>47577</v>
+      </c>
+      <c r="B185" t="s">
+        <v>849</v>
+      </c>
+      <c r="C185" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186">
         <v>48098</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B186" t="s">
         <v>850</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C186" t="s">
         <v>802</v>
       </c>
     </row>
@@ -11333,18 +11482,1876 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:C372"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="1"/>
-    <col min="2" max="2" width="42.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1"/>
-    <col min="4" max="4" width="31" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="1"/>
-    <col min="6" max="6" width="33.7109375" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="12.5703125" style="1"/>
+    <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="12.5703125" style="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1"/>
+      <c r="B1"/>
+      <c r="C1"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34"/>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+    </row>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38"/>
+    </row>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40"/>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45"/>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46"/>
+    </row>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47"/>
+    </row>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48"/>
+      <c r="B48"/>
+      <c r="C48"/>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49"/>
+      <c r="B49"/>
+      <c r="C49"/>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50"/>
+      <c r="B50"/>
+      <c r="C50"/>
+    </row>
+    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51"/>
+      <c r="B51"/>
+      <c r="C51"/>
+    </row>
+    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52"/>
+      <c r="B52"/>
+      <c r="C52"/>
+    </row>
+    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+    </row>
+    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+    </row>
+    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55"/>
+      <c r="B55"/>
+      <c r="C55"/>
+    </row>
+    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+    </row>
+    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57"/>
+      <c r="B57"/>
+      <c r="C57"/>
+    </row>
+    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58"/>
+      <c r="B58"/>
+      <c r="C58"/>
+    </row>
+    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59"/>
+      <c r="B59"/>
+      <c r="C59"/>
+    </row>
+    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60"/>
+    </row>
+    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61"/>
+    </row>
+    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62"/>
+      <c r="B62"/>
+      <c r="C62"/>
+    </row>
+    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63"/>
+      <c r="B63"/>
+      <c r="C63"/>
+    </row>
+    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64"/>
+      <c r="B64"/>
+      <c r="C64"/>
+    </row>
+    <row r="65" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65"/>
+      <c r="B65"/>
+      <c r="C65"/>
+    </row>
+    <row r="66" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66"/>
+      <c r="B66"/>
+      <c r="C66"/>
+    </row>
+    <row r="67" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67"/>
+    </row>
+    <row r="68" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68"/>
+      <c r="B68"/>
+      <c r="C68"/>
+    </row>
+    <row r="69" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69"/>
+      <c r="B69"/>
+      <c r="C69"/>
+    </row>
+    <row r="70" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70"/>
+      <c r="B70"/>
+      <c r="C70"/>
+    </row>
+    <row r="71" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71"/>
+    </row>
+    <row r="72" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72"/>
+      <c r="B72"/>
+      <c r="C72"/>
+    </row>
+    <row r="73" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73"/>
+      <c r="B73"/>
+      <c r="C73"/>
+    </row>
+    <row r="74" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74"/>
+      <c r="B74"/>
+      <c r="C74"/>
+    </row>
+    <row r="75" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75"/>
+    </row>
+    <row r="76" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76"/>
+      <c r="B76"/>
+      <c r="C76"/>
+    </row>
+    <row r="77" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77"/>
+    </row>
+    <row r="78" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78"/>
+      <c r="B78"/>
+      <c r="C78"/>
+    </row>
+    <row r="79" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79"/>
+      <c r="B79"/>
+      <c r="C79"/>
+    </row>
+    <row r="80" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80"/>
+      <c r="B80"/>
+      <c r="C80"/>
+    </row>
+    <row r="81" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81"/>
+    </row>
+    <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+    </row>
+    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83"/>
+    </row>
+    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84"/>
+    </row>
+    <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85"/>
+      <c r="B85"/>
+      <c r="C85"/>
+    </row>
+    <row r="86" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86"/>
+      <c r="B86"/>
+      <c r="C86"/>
+    </row>
+    <row r="87" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+    </row>
+    <row r="88" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88"/>
+      <c r="B88"/>
+      <c r="C88"/>
+    </row>
+    <row r="89" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89"/>
+    </row>
+    <row r="90" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90"/>
+      <c r="B90"/>
+      <c r="C90"/>
+    </row>
+    <row r="91" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+    </row>
+    <row r="92" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92"/>
+    </row>
+    <row r="93" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93"/>
+      <c r="B93"/>
+      <c r="C93"/>
+    </row>
+    <row r="94" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94"/>
+    </row>
+    <row r="95" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95"/>
+      <c r="B95"/>
+      <c r="C95"/>
+    </row>
+    <row r="96" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96"/>
+      <c r="B96"/>
+      <c r="C96"/>
+    </row>
+    <row r="97" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97"/>
+    </row>
+    <row r="98" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98"/>
+    </row>
+    <row r="99" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+    </row>
+    <row r="100" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+    </row>
+    <row r="101" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+    </row>
+    <row r="102" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+    </row>
+    <row r="103" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+    </row>
+    <row r="104" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+    </row>
+    <row r="105" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+    </row>
+    <row r="106" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+    </row>
+    <row r="107" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+    </row>
+    <row r="108" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+    </row>
+    <row r="109" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+    </row>
+    <row r="110" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+    </row>
+    <row r="111" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+    </row>
+    <row r="112" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+    </row>
+    <row r="113" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+    </row>
+    <row r="114" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+    </row>
+    <row r="115" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115"/>
+      <c r="B115"/>
+      <c r="C115"/>
+    </row>
+    <row r="116" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116"/>
+      <c r="B116"/>
+      <c r="C116"/>
+    </row>
+    <row r="117" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+    </row>
+    <row r="118" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
+    </row>
+    <row r="119" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119"/>
+    </row>
+    <row r="120" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+    </row>
+    <row r="121" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
+    </row>
+    <row r="122" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+    </row>
+    <row r="123" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123"/>
+    </row>
+    <row r="124" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124"/>
+      <c r="B124"/>
+      <c r="C124"/>
+    </row>
+    <row r="125" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125"/>
+      <c r="B125"/>
+      <c r="C125"/>
+    </row>
+    <row r="126" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126"/>
+      <c r="B126"/>
+      <c r="C126"/>
+    </row>
+    <row r="127" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127"/>
+      <c r="B127"/>
+      <c r="C127"/>
+    </row>
+    <row r="128" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128"/>
+      <c r="B128"/>
+      <c r="C128"/>
+    </row>
+    <row r="129" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129"/>
+      <c r="B129"/>
+      <c r="C129"/>
+    </row>
+    <row r="130" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130"/>
+      <c r="B130"/>
+      <c r="C130"/>
+    </row>
+    <row r="131" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131"/>
+      <c r="B131"/>
+      <c r="C131"/>
+    </row>
+    <row r="132" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132"/>
+      <c r="B132"/>
+      <c r="C132"/>
+    </row>
+    <row r="133" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133"/>
+      <c r="B133"/>
+      <c r="C133"/>
+    </row>
+    <row r="134" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134"/>
+      <c r="B134"/>
+      <c r="C134"/>
+    </row>
+    <row r="135" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135"/>
+      <c r="B135"/>
+      <c r="C135"/>
+    </row>
+    <row r="136" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136"/>
+      <c r="B136"/>
+      <c r="C136"/>
+    </row>
+    <row r="137" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137"/>
+      <c r="B137"/>
+      <c r="C137"/>
+    </row>
+    <row r="138" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138"/>
+      <c r="B138"/>
+      <c r="C138"/>
+    </row>
+    <row r="139" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139"/>
+      <c r="B139"/>
+      <c r="C139"/>
+    </row>
+    <row r="140" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140"/>
+      <c r="B140"/>
+      <c r="C140"/>
+    </row>
+    <row r="141" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141"/>
+      <c r="B141"/>
+      <c r="C141"/>
+    </row>
+    <row r="142" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142"/>
+      <c r="B142"/>
+      <c r="C142"/>
+    </row>
+    <row r="143" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143"/>
+      <c r="B143"/>
+      <c r="C143"/>
+    </row>
+    <row r="144" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144"/>
+      <c r="B144"/>
+      <c r="C144"/>
+    </row>
+    <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145"/>
+      <c r="B145"/>
+      <c r="C145"/>
+    </row>
+    <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146"/>
+      <c r="B146"/>
+      <c r="C146"/>
+    </row>
+    <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147"/>
+      <c r="B147"/>
+      <c r="C147"/>
+    </row>
+    <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148"/>
+      <c r="B148"/>
+      <c r="C148"/>
+    </row>
+    <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149"/>
+      <c r="B149"/>
+      <c r="C149"/>
+    </row>
+    <row r="150" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150"/>
+      <c r="B150"/>
+      <c r="C150"/>
+    </row>
+    <row r="151" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151"/>
+      <c r="B151"/>
+      <c r="C151"/>
+    </row>
+    <row r="152" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152"/>
+      <c r="B152"/>
+      <c r="C152"/>
+    </row>
+    <row r="153" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153"/>
+      <c r="B153"/>
+      <c r="C153"/>
+    </row>
+    <row r="154" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154"/>
+      <c r="B154"/>
+      <c r="C154"/>
+    </row>
+    <row r="155" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155"/>
+      <c r="B155"/>
+      <c r="C155"/>
+    </row>
+    <row r="156" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156"/>
+      <c r="B156"/>
+      <c r="C156"/>
+    </row>
+    <row r="157" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157"/>
+      <c r="B157"/>
+      <c r="C157"/>
+    </row>
+    <row r="158" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158"/>
+      <c r="B158"/>
+      <c r="C158"/>
+    </row>
+    <row r="159" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159"/>
+      <c r="B159"/>
+      <c r="C159"/>
+    </row>
+    <row r="160" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160"/>
+      <c r="B160"/>
+      <c r="C160"/>
+    </row>
+    <row r="161" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161"/>
+      <c r="B161"/>
+      <c r="C161"/>
+    </row>
+    <row r="162" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162"/>
+      <c r="B162"/>
+      <c r="C162"/>
+    </row>
+    <row r="163" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163"/>
+      <c r="B163"/>
+      <c r="C163"/>
+    </row>
+    <row r="164" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164"/>
+      <c r="B164"/>
+      <c r="C164"/>
+    </row>
+    <row r="165" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165"/>
+      <c r="B165"/>
+      <c r="C165"/>
+    </row>
+    <row r="166" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166"/>
+      <c r="B166"/>
+      <c r="C166"/>
+    </row>
+    <row r="167" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167"/>
+      <c r="B167"/>
+      <c r="C167"/>
+    </row>
+    <row r="168" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168"/>
+      <c r="B168"/>
+      <c r="C168"/>
+    </row>
+    <row r="169" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169"/>
+      <c r="B169"/>
+      <c r="C169"/>
+    </row>
+    <row r="170" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170"/>
+      <c r="B170"/>
+      <c r="C170"/>
+    </row>
+    <row r="171" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171"/>
+      <c r="B171"/>
+      <c r="C171"/>
+    </row>
+    <row r="172" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172"/>
+      <c r="B172"/>
+      <c r="C172"/>
+    </row>
+    <row r="173" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173"/>
+      <c r="B173"/>
+      <c r="C173"/>
+    </row>
+    <row r="174" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174"/>
+      <c r="B174"/>
+      <c r="C174"/>
+    </row>
+    <row r="175" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175"/>
+      <c r="B175"/>
+      <c r="C175"/>
+    </row>
+    <row r="176" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176"/>
+      <c r="B176"/>
+      <c r="C176"/>
+    </row>
+    <row r="177" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177"/>
+      <c r="B177"/>
+      <c r="C177"/>
+    </row>
+    <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178"/>
+      <c r="B178"/>
+      <c r="C178"/>
+    </row>
+    <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179"/>
+      <c r="B179"/>
+      <c r="C179"/>
+    </row>
+    <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180"/>
+      <c r="B180"/>
+      <c r="C180"/>
+    </row>
+    <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181"/>
+      <c r="B181"/>
+      <c r="C181"/>
+    </row>
+    <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182"/>
+      <c r="B182"/>
+      <c r="C182"/>
+    </row>
+    <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183"/>
+      <c r="B183"/>
+      <c r="C183"/>
+    </row>
+    <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184"/>
+      <c r="B184"/>
+      <c r="C184"/>
+    </row>
+    <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185"/>
+      <c r="B185"/>
+      <c r="C185"/>
+    </row>
+    <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186"/>
+      <c r="B186"/>
+      <c r="C186"/>
+    </row>
+    <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187"/>
+      <c r="B187"/>
+      <c r="C187"/>
+    </row>
+    <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188"/>
+      <c r="B188"/>
+      <c r="C188"/>
+    </row>
+    <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189"/>
+      <c r="B189"/>
+      <c r="C189"/>
+    </row>
+    <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190"/>
+      <c r="B190"/>
+      <c r="C190"/>
+    </row>
+    <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191"/>
+      <c r="B191"/>
+      <c r="C191"/>
+    </row>
+    <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192"/>
+      <c r="B192"/>
+      <c r="C192"/>
+    </row>
+    <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193"/>
+      <c r="B193"/>
+      <c r="C193"/>
+    </row>
+    <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194"/>
+      <c r="B194"/>
+      <c r="C194"/>
+    </row>
+    <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195"/>
+      <c r="B195"/>
+      <c r="C195"/>
+    </row>
+    <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196"/>
+      <c r="B196"/>
+      <c r="C196"/>
+    </row>
+    <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197"/>
+      <c r="B197"/>
+      <c r="C197"/>
+    </row>
+    <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198"/>
+      <c r="B198"/>
+      <c r="C198"/>
+    </row>
+    <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199"/>
+      <c r="B199"/>
+      <c r="C199"/>
+    </row>
+    <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200"/>
+      <c r="B200"/>
+      <c r="C200"/>
+    </row>
+    <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201"/>
+      <c r="B201"/>
+      <c r="C201"/>
+    </row>
+    <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202"/>
+      <c r="B202"/>
+      <c r="C202"/>
+    </row>
+    <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203"/>
+      <c r="B203"/>
+      <c r="C203"/>
+    </row>
+    <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204"/>
+      <c r="B204"/>
+      <c r="C204"/>
+    </row>
+    <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205"/>
+      <c r="B205"/>
+      <c r="C205"/>
+    </row>
+    <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206"/>
+      <c r="B206"/>
+      <c r="C206"/>
+    </row>
+    <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207"/>
+      <c r="B207"/>
+      <c r="C207"/>
+    </row>
+    <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208"/>
+      <c r="B208"/>
+      <c r="C208"/>
+    </row>
+    <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209"/>
+      <c r="B209"/>
+      <c r="C209"/>
+    </row>
+    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210"/>
+      <c r="B210"/>
+      <c r="C210"/>
+    </row>
+    <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211"/>
+      <c r="B211"/>
+      <c r="C211"/>
+    </row>
+    <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212"/>
+      <c r="B212"/>
+      <c r="C212"/>
+    </row>
+    <row r="213" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213"/>
+      <c r="B213"/>
+      <c r="C213"/>
+    </row>
+    <row r="214" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214"/>
+      <c r="B214"/>
+      <c r="C214"/>
+    </row>
+    <row r="215" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215"/>
+      <c r="B215"/>
+      <c r="C215"/>
+    </row>
+    <row r="216" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216"/>
+      <c r="B216"/>
+      <c r="C216"/>
+    </row>
+    <row r="217" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217"/>
+      <c r="B217"/>
+      <c r="C217"/>
+    </row>
+    <row r="218" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218"/>
+      <c r="B218"/>
+      <c r="C218"/>
+    </row>
+    <row r="219" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219"/>
+      <c r="B219"/>
+      <c r="C219"/>
+    </row>
+    <row r="220" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220"/>
+      <c r="B220"/>
+      <c r="C220"/>
+    </row>
+    <row r="221" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221"/>
+      <c r="B221"/>
+      <c r="C221"/>
+    </row>
+    <row r="222" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222"/>
+      <c r="B222"/>
+      <c r="C222"/>
+    </row>
+    <row r="223" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223"/>
+      <c r="B223"/>
+      <c r="C223"/>
+    </row>
+    <row r="224" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224"/>
+      <c r="B224"/>
+      <c r="C224"/>
+    </row>
+    <row r="225" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225"/>
+      <c r="B225"/>
+      <c r="C225"/>
+    </row>
+    <row r="226" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226"/>
+      <c r="B226"/>
+      <c r="C226"/>
+    </row>
+    <row r="227" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227"/>
+      <c r="B227"/>
+      <c r="C227"/>
+    </row>
+    <row r="228" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228"/>
+      <c r="B228"/>
+      <c r="C228"/>
+    </row>
+    <row r="229" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229"/>
+      <c r="B229"/>
+      <c r="C229"/>
+    </row>
+    <row r="230" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230"/>
+      <c r="B230"/>
+      <c r="C230"/>
+    </row>
+    <row r="231" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231"/>
+      <c r="B231"/>
+      <c r="C231"/>
+    </row>
+    <row r="232" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232"/>
+      <c r="B232"/>
+      <c r="C232"/>
+    </row>
+    <row r="233" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233"/>
+      <c r="B233"/>
+      <c r="C233"/>
+    </row>
+    <row r="234" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234"/>
+      <c r="B234"/>
+      <c r="C234"/>
+    </row>
+    <row r="235" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235"/>
+      <c r="B235"/>
+      <c r="C235"/>
+    </row>
+    <row r="236" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236"/>
+      <c r="B236"/>
+      <c r="C236"/>
+    </row>
+    <row r="237" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237"/>
+      <c r="B237"/>
+      <c r="C237"/>
+    </row>
+    <row r="238" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238"/>
+      <c r="B238"/>
+      <c r="C238"/>
+    </row>
+    <row r="239" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239"/>
+      <c r="B239"/>
+      <c r="C239"/>
+    </row>
+    <row r="240" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240"/>
+      <c r="B240"/>
+      <c r="C240"/>
+    </row>
+    <row r="241" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241"/>
+      <c r="B241"/>
+      <c r="C241"/>
+    </row>
+    <row r="242" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242"/>
+      <c r="B242"/>
+      <c r="C242"/>
+    </row>
+    <row r="243" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243"/>
+      <c r="B243"/>
+      <c r="C243"/>
+    </row>
+    <row r="244" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244"/>
+      <c r="B244"/>
+      <c r="C244"/>
+    </row>
+    <row r="245" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245"/>
+      <c r="B245"/>
+      <c r="C245"/>
+    </row>
+    <row r="246" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246"/>
+      <c r="B246"/>
+      <c r="C246"/>
+    </row>
+    <row r="247" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247"/>
+      <c r="B247"/>
+      <c r="C247"/>
+    </row>
+    <row r="248" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248"/>
+      <c r="B248"/>
+      <c r="C248"/>
+    </row>
+    <row r="249" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249"/>
+      <c r="B249"/>
+      <c r="C249"/>
+    </row>
+    <row r="250" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250"/>
+      <c r="B250"/>
+      <c r="C250"/>
+    </row>
+    <row r="251" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251"/>
+      <c r="B251"/>
+      <c r="C251"/>
+    </row>
+    <row r="252" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252"/>
+      <c r="B252"/>
+      <c r="C252"/>
+    </row>
+    <row r="253" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253"/>
+      <c r="B253"/>
+      <c r="C253"/>
+    </row>
+    <row r="254" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254"/>
+      <c r="B254"/>
+      <c r="C254"/>
+    </row>
+    <row r="255" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255"/>
+      <c r="B255"/>
+      <c r="C255"/>
+    </row>
+    <row r="256" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256"/>
+      <c r="B256"/>
+      <c r="C256"/>
+    </row>
+    <row r="257" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257"/>
+      <c r="B257"/>
+      <c r="C257"/>
+    </row>
+    <row r="258" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258"/>
+      <c r="B258"/>
+      <c r="C258"/>
+    </row>
+    <row r="259" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259"/>
+      <c r="B259"/>
+      <c r="C259"/>
+    </row>
+    <row r="260" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260"/>
+      <c r="B260"/>
+      <c r="C260"/>
+    </row>
+    <row r="261" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261"/>
+      <c r="B261"/>
+      <c r="C261"/>
+    </row>
+    <row r="262" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262"/>
+      <c r="B262"/>
+      <c r="C262"/>
+    </row>
+    <row r="263" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263"/>
+      <c r="B263"/>
+      <c r="C263"/>
+    </row>
+    <row r="264" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264"/>
+      <c r="B264"/>
+      <c r="C264"/>
+    </row>
+    <row r="265" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A265"/>
+      <c r="B265"/>
+      <c r="C265"/>
+    </row>
+    <row r="266" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A266"/>
+      <c r="B266"/>
+      <c r="C266"/>
+    </row>
+    <row r="267" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267"/>
+      <c r="B267"/>
+      <c r="C267"/>
+    </row>
+    <row r="268" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268"/>
+      <c r="B268"/>
+      <c r="C268"/>
+    </row>
+    <row r="269" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269"/>
+      <c r="B269"/>
+      <c r="C269"/>
+    </row>
+    <row r="270" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270"/>
+      <c r="B270"/>
+      <c r="C270"/>
+    </row>
+    <row r="271" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271"/>
+      <c r="B271"/>
+      <c r="C271"/>
+    </row>
+    <row r="272" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272"/>
+      <c r="B272"/>
+      <c r="C272"/>
+    </row>
+    <row r="273" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273"/>
+      <c r="B273"/>
+      <c r="C273"/>
+    </row>
+    <row r="274" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A274"/>
+      <c r="B274"/>
+      <c r="C274"/>
+    </row>
+    <row r="275" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275"/>
+      <c r="B275"/>
+      <c r="C275"/>
+    </row>
+    <row r="276" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276"/>
+      <c r="B276"/>
+      <c r="C276"/>
+    </row>
+    <row r="277" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A277"/>
+      <c r="B277"/>
+      <c r="C277"/>
+    </row>
+    <row r="278" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278"/>
+      <c r="B278"/>
+      <c r="C278"/>
+    </row>
+    <row r="279" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279"/>
+      <c r="B279"/>
+      <c r="C279"/>
+    </row>
+    <row r="280" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280"/>
+      <c r="B280"/>
+      <c r="C280"/>
+    </row>
+    <row r="281" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281"/>
+      <c r="B281"/>
+      <c r="C281"/>
+    </row>
+    <row r="282" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282"/>
+      <c r="B282"/>
+      <c r="C282"/>
+    </row>
+    <row r="283" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283"/>
+      <c r="B283"/>
+      <c r="C283"/>
+    </row>
+    <row r="284" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284"/>
+      <c r="B284"/>
+      <c r="C284"/>
+    </row>
+    <row r="285" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285"/>
+      <c r="B285"/>
+      <c r="C285"/>
+    </row>
+    <row r="286" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286"/>
+      <c r="B286"/>
+      <c r="C286"/>
+    </row>
+    <row r="287" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A287"/>
+      <c r="B287"/>
+      <c r="C287"/>
+    </row>
+    <row r="288" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288"/>
+      <c r="B288"/>
+      <c r="C288"/>
+    </row>
+    <row r="289" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A289"/>
+      <c r="B289"/>
+      <c r="C289"/>
+    </row>
+    <row r="290" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290"/>
+      <c r="B290"/>
+      <c r="C290"/>
+    </row>
+    <row r="291" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291"/>
+      <c r="B291"/>
+      <c r="C291"/>
+    </row>
+    <row r="292" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A292"/>
+      <c r="B292"/>
+      <c r="C292"/>
+    </row>
+    <row r="293" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293"/>
+      <c r="B293"/>
+      <c r="C293"/>
+    </row>
+    <row r="294" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294"/>
+      <c r="B294"/>
+      <c r="C294"/>
+    </row>
+    <row r="295" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295"/>
+      <c r="B295"/>
+      <c r="C295"/>
+    </row>
+    <row r="296" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296"/>
+      <c r="B296"/>
+      <c r="C296"/>
+    </row>
+    <row r="297" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297"/>
+      <c r="B297"/>
+      <c r="C297"/>
+    </row>
+    <row r="298" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298"/>
+      <c r="B298"/>
+      <c r="C298"/>
+    </row>
+    <row r="299" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299"/>
+      <c r="B299"/>
+      <c r="C299"/>
+    </row>
+    <row r="300" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300"/>
+      <c r="B300"/>
+      <c r="C300"/>
+    </row>
+    <row r="301" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301"/>
+      <c r="B301"/>
+      <c r="C301"/>
+    </row>
+    <row r="302" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302"/>
+      <c r="B302"/>
+      <c r="C302"/>
+    </row>
+    <row r="303" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303"/>
+      <c r="B303"/>
+      <c r="C303"/>
+    </row>
+    <row r="304" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A304"/>
+      <c r="B304"/>
+      <c r="C304"/>
+    </row>
+    <row r="305" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305"/>
+      <c r="B305"/>
+      <c r="C305"/>
+    </row>
+    <row r="306" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A306"/>
+      <c r="B306"/>
+      <c r="C306"/>
+    </row>
+    <row r="307" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A307"/>
+      <c r="B307"/>
+      <c r="C307"/>
+    </row>
+    <row r="308" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308"/>
+      <c r="B308"/>
+      <c r="C308"/>
+    </row>
+    <row r="309" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A309"/>
+      <c r="B309"/>
+      <c r="C309"/>
+    </row>
+    <row r="310" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A310"/>
+      <c r="B310"/>
+      <c r="C310"/>
+    </row>
+    <row r="311" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A311"/>
+      <c r="B311"/>
+      <c r="C311"/>
+    </row>
+    <row r="312" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A312"/>
+      <c r="B312"/>
+      <c r="C312"/>
+    </row>
+    <row r="313" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A313"/>
+      <c r="B313"/>
+      <c r="C313"/>
+    </row>
+    <row r="314" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314"/>
+      <c r="B314"/>
+      <c r="C314"/>
+    </row>
+    <row r="315" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315"/>
+      <c r="B315"/>
+      <c r="C315"/>
+    </row>
+    <row r="316" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A316"/>
+      <c r="B316"/>
+      <c r="C316"/>
+    </row>
+    <row r="317" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A317"/>
+      <c r="B317"/>
+      <c r="C317"/>
+    </row>
+    <row r="318" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A318"/>
+      <c r="B318"/>
+      <c r="C318"/>
+    </row>
+    <row r="319" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319"/>
+      <c r="B319"/>
+      <c r="C319"/>
+    </row>
+    <row r="320" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A320"/>
+      <c r="B320"/>
+      <c r="C320"/>
+    </row>
+    <row r="321" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A321"/>
+      <c r="B321"/>
+      <c r="C321"/>
+    </row>
+    <row r="322" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322"/>
+      <c r="B322"/>
+      <c r="C322"/>
+    </row>
+    <row r="323" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323"/>
+      <c r="B323"/>
+      <c r="C323"/>
+    </row>
+    <row r="324" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A324"/>
+      <c r="B324"/>
+      <c r="C324"/>
+    </row>
+    <row r="325" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325"/>
+      <c r="B325"/>
+      <c r="C325"/>
+    </row>
+    <row r="326" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A326"/>
+      <c r="B326"/>
+      <c r="C326"/>
+    </row>
+    <row r="327" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327"/>
+      <c r="B327"/>
+      <c r="C327"/>
+    </row>
+    <row r="328" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328"/>
+      <c r="B328"/>
+      <c r="C328"/>
+    </row>
+    <row r="329" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A329"/>
+      <c r="B329"/>
+      <c r="C329"/>
+    </row>
+    <row r="330" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A330"/>
+      <c r="B330"/>
+      <c r="C330"/>
+    </row>
+    <row r="331" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A331"/>
+      <c r="B331"/>
+      <c r="C331"/>
+    </row>
+    <row r="332" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A332"/>
+      <c r="B332"/>
+      <c r="C332"/>
+    </row>
+    <row r="333" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A333"/>
+      <c r="B333"/>
+      <c r="C333"/>
+    </row>
+    <row r="334" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A334"/>
+      <c r="B334"/>
+      <c r="C334"/>
+    </row>
+    <row r="335" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A335"/>
+      <c r="B335"/>
+      <c r="C335"/>
+    </row>
+    <row r="336" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A336"/>
+      <c r="B336"/>
+      <c r="C336"/>
+    </row>
+    <row r="337" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A337"/>
+      <c r="B337"/>
+      <c r="C337"/>
+    </row>
+    <row r="338" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A338"/>
+      <c r="B338"/>
+      <c r="C338"/>
+    </row>
+    <row r="339" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A339"/>
+      <c r="B339"/>
+      <c r="C339"/>
+    </row>
+    <row r="340" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A340"/>
+      <c r="B340"/>
+      <c r="C340"/>
+    </row>
+    <row r="341" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A341"/>
+      <c r="B341"/>
+      <c r="C341"/>
+    </row>
+    <row r="342" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A342"/>
+      <c r="B342"/>
+      <c r="C342"/>
+    </row>
+    <row r="343" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A343"/>
+      <c r="B343"/>
+      <c r="C343"/>
+    </row>
+    <row r="344" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A344"/>
+      <c r="B344"/>
+      <c r="C344"/>
+    </row>
+    <row r="345" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A345"/>
+      <c r="B345"/>
+      <c r="C345"/>
+    </row>
+    <row r="346" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A346"/>
+      <c r="B346"/>
+      <c r="C346"/>
+    </row>
+    <row r="347" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A347"/>
+      <c r="B347"/>
+      <c r="C347"/>
+    </row>
+    <row r="348" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A348"/>
+      <c r="B348"/>
+      <c r="C348"/>
+    </row>
+    <row r="349" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A349"/>
+      <c r="B349"/>
+      <c r="C349"/>
+    </row>
+    <row r="350" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A350"/>
+      <c r="B350"/>
+      <c r="C350"/>
+    </row>
+    <row r="351" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A351"/>
+      <c r="B351"/>
+      <c r="C351"/>
+    </row>
+    <row r="352" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A352"/>
+      <c r="B352"/>
+      <c r="C352"/>
+    </row>
+    <row r="353" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A353"/>
+      <c r="B353"/>
+      <c r="C353"/>
+    </row>
+    <row r="354" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A354"/>
+      <c r="B354"/>
+      <c r="C354"/>
+    </row>
+    <row r="355" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A355"/>
+      <c r="B355"/>
+      <c r="C355"/>
+    </row>
+    <row r="356" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A356"/>
+      <c r="B356"/>
+      <c r="C356"/>
+    </row>
+    <row r="357" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A357"/>
+      <c r="B357"/>
+      <c r="C357"/>
+    </row>
+    <row r="358" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A358"/>
+      <c r="B358"/>
+      <c r="C358"/>
+    </row>
+    <row r="359" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A359"/>
+      <c r="B359"/>
+      <c r="C359"/>
+    </row>
+    <row r="360" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A360"/>
+      <c r="B360"/>
+      <c r="C360"/>
+    </row>
+    <row r="361" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A361"/>
+      <c r="B361"/>
+      <c r="C361"/>
+    </row>
+    <row r="362" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A362"/>
+      <c r="B362"/>
+      <c r="C362"/>
+    </row>
+    <row r="363" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A363"/>
+      <c r="B363"/>
+      <c r="C363"/>
+    </row>
+    <row r="364" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A364"/>
+      <c r="B364"/>
+      <c r="C364"/>
+    </row>
+    <row r="365" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A365"/>
+      <c r="B365"/>
+      <c r="C365"/>
+    </row>
+    <row r="366" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A366"/>
+      <c r="B366"/>
+      <c r="C366"/>
+    </row>
+    <row r="367" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A367"/>
+      <c r="B367"/>
+      <c r="C367"/>
+    </row>
+    <row r="368" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A368"/>
+      <c r="B368"/>
+      <c r="C368"/>
+    </row>
+    <row r="369" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A369"/>
+      <c r="B369"/>
+      <c r="C369"/>
+    </row>
+    <row r="370" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A370"/>
+      <c r="B370"/>
+      <c r="C370"/>
+    </row>
+    <row r="371" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A371"/>
+      <c r="B371"/>
+      <c r="C371"/>
+    </row>
+    <row r="372" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A372"/>
+      <c r="B372"/>
+      <c r="C372"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>